--- a/sheets/조재수대금교본/검수/토방 마루-2.xlsx
+++ b/sheets/조재수대금교본/검수/토방 마루-2.xlsx
@@ -4445,7 +4445,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -4458,7 +4458,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰ㄷ</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -4471,14 +4471,14 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅅ
+          <t xml:space="preserve">太
 –</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太ㅅ
+          <t xml:space="preserve">太
 –</t>
         </is>
       </c>
@@ -4575,27 +4575,18 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="C6" s="24"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D6" s="21"/>
       <c r="E6" s="24"/>
-      <c r="F6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F6" s="21"/>
       <c r="G6" s="24"/>
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢ﾉ</t>
+–潢</t>
         </is>
       </c>
       <c r="I6" s="24"/>
@@ -4608,20 +4599,15 @@
       <c r="K6" s="24"/>
       <c r="L6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰
-‹</t>
+          <t xml:space="preserve">汰</t>
         </is>
       </c>
       <c r="M6" s="24"/>
-      <c r="N6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N6" s="21"/>
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太∧
+          <t xml:space="preserve">太
 仲</t>
         </is>
       </c>
@@ -4667,8 +4653,7 @@
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -4768,58 +4753,25 @@
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C10" s="24"/>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D10" s="21"/>
       <c r="E10" s="24"/>
-      <c r="F10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F10" s="21"/>
       <c r="G10" s="24"/>
-      <c r="H10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H10" s="21"/>
       <c r="I10" s="24"/>
-      <c r="J10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J10" s="21"/>
       <c r="K10" s="24"/>
-      <c r="L10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="L10" s="21"/>
       <c r="M10" s="24"/>
-      <c r="N10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N10" s="21"/>
       <c r="O10" s="24"/>
-      <c r="P10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="P10" s="21"/>
       <c r="Q10" s="24"/>
-      <c r="R10" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="R10" s="21"/>
       <c r="S10" s="24"/>
     </row>
     <row r="11" ht="97.23" customHeight="true">
@@ -4999,29 +4951,25 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳
-‹</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="C14" s="24"/>
       <c r="D14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋
-‹</t>
+          <t xml:space="preserve">淋</t>
         </is>
       </c>
       <c r="E14" s="24"/>
       <c r="F14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="G14" s="24"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="I14" s="24"/>
@@ -5034,15 +4982,13 @@
       <c r="K14" s="24"/>
       <c r="L14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="M14" s="24"/>
       <c r="N14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-‹</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="O14" s="24"/>
@@ -5068,22 +5014,20 @@
       <c r="D15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
-–淋·
-‹</t>
+–淋·</t>
         </is>
       </c>
       <c r="E15" s="22"/>
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="G15" s="22"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢
-ﾉ</t>
+          <t xml:space="preserve">潢</t>
         </is>
       </c>
       <c r="I15" s="22"/>
@@ -5103,7 +5047,7 @@
       <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–⌝</t>
+–</t>
         </is>
       </c>
       <c r="O15" s="22"/>
@@ -5116,9 +5060,8 @@
       <c r="Q15" s="22"/>
       <c r="R15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑲∧
-黃
-ﾉ</t>
+          <t xml:space="preserve">㑲
+黃</t>
         </is>
       </c>
       <c r="S15" s="22"/>
@@ -5133,7 +5076,7 @@
       <c r="C16" s="23"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳∽</t>
+          <t xml:space="preserve">湳</t>
         </is>
       </c>
       <c r="E16" s="23"/>
@@ -5202,29 +5145,13 @@
         </is>
       </c>
       <c r="C18" s="24"/>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="D18" s="21"/>
       <c r="E18" s="24"/>
-      <c r="F18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="F18" s="21"/>
       <c r="G18" s="24"/>
-      <c r="H18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H18" s="21"/>
       <c r="I18" s="24"/>
-      <c r="J18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="J18" s="21"/>
       <c r="K18" s="24"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
@@ -5233,11 +5160,7 @@
         </is>
       </c>
       <c r="M18" s="24"/>
-      <c r="N18" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="N18" s="21"/>
       <c r="O18" s="24"/>
       <c r="P18" s="21"/>
       <c r="Q18" s="24"/>

--- a/sheets/조재수대금교본/검수/토방 마루-2.xlsx
+++ b/sheets/조재수대금교본/검수/토방 마루-2.xlsx
@@ -4445,7 +4445,7 @@
       <c r="G3" s="22"/>
       <c r="H3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="I3" s="22"/>
@@ -4458,7 +4458,7 @@
       <c r="K3" s="22"/>
       <c r="L3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰</t>
+          <t xml:space="preserve">汰ㄷ</t>
         </is>
       </c>
       <c r="M3" s="22"/>
@@ -4471,14 +4471,14 @@
       <c r="O3" s="22"/>
       <c r="P3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ㅅ
 –</t>
         </is>
       </c>
       <c r="Q3" s="22"/>
       <c r="R3" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太ㅅ
 –</t>
         </is>
       </c>
@@ -4586,7 +4586,7 @@
       <c r="H6" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–潢</t>
+–潢ﾉ</t>
         </is>
       </c>
       <c r="I6" s="24"/>
@@ -4607,7 +4607,7 @@
       <c r="O6" s="24"/>
       <c r="P6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
+          <t xml:space="preserve">太∧
 仲</t>
         </is>
       </c>
@@ -4653,7 +4653,8 @@
       <c r="K7" s="22"/>
       <c r="L7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="M7" s="22"/>
@@ -5021,13 +5022,14 @@
       <c r="F15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="G15" s="22"/>
       <c r="H15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢</t>
+          <t xml:space="preserve">潢
+ﾉ</t>
         </is>
       </c>
       <c r="I15" s="22"/>
@@ -5047,7 +5049,7 @@
       <c r="N15" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-–</t>
+–⌝</t>
         </is>
       </c>
       <c r="O15" s="22"/>
@@ -5060,8 +5062,9 @@
       <c r="Q15" s="22"/>
       <c r="R15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㑲
-黃</t>
+          <t xml:space="preserve">㑲∧
+黃
+ﾉ</t>
         </is>
       </c>
       <c r="S15" s="22"/>
@@ -5076,7 +5079,7 @@
       <c r="C16" s="23"/>
       <c r="D16" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳</t>
+          <t xml:space="preserve">湳∽</t>
         </is>
       </c>
       <c r="E16" s="23"/>

--- a/sheets/조재수대금교본/검수/토방 마루-2.xlsx
+++ b/sheets/조재수대금교본/검수/토방 마루-2.xlsx
@@ -4372,30 +4372,30 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="13.46" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="13.46" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="13.46" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="13.46" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
+    <col min="14" max="14" width="13.46" customWidth="1"/>
     <col min="15" max="15" width="6" customWidth="1"/>
-    <col min="16" max="16" width="9" customWidth="1"/>
+    <col min="16" max="16" width="13.46" customWidth="1"/>
     <col min="17" max="17" width="6" customWidth="1"/>
-    <col min="18" max="18" width="9" customWidth="1"/>
+    <col min="18" max="18" width="13.46" customWidth="1"/>
     <col min="19" max="19" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="86.96" customHeight="true">
+    <row r="2" ht="83.33" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -4420,7 +4420,7 @@
       <c r="R2" s="20"/>
       <c r="S2" s="20"/>
     </row>
-    <row r="3" ht="97.23" customHeight="true">
+    <row r="3" ht="93.16" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -4484,7 +4484,7 @@
       </c>
       <c r="S3" s="22"/>
     </row>
-    <row r="4" ht="97.23" customHeight="true">
+    <row r="4" ht="93.16" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -4530,7 +4530,7 @@
       <c r="R4" s="21"/>
       <c r="S4" s="23"/>
     </row>
-    <row r="5" ht="97.23" customHeight="true">
+    <row r="5" ht="93.16" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
       <c r="R5" s="21"/>
       <c r="S5" s="23"/>
     </row>
-    <row r="6" ht="97.23" customHeight="true">
+    <row r="6" ht="93.16" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -4615,7 +4615,7 @@
       <c r="R6" s="21"/>
       <c r="S6" s="24"/>
     </row>
-    <row r="7" ht="97.23" customHeight="true">
+    <row r="7" ht="93.16" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="S7" s="22"/>
     </row>
-    <row r="8" ht="97.23" customHeight="true">
+    <row r="8" ht="93.16" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="S8" s="23"/>
     </row>
-    <row r="9" ht="97.23" customHeight="true">
+    <row r="9" ht="93.16" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -4750,7 +4750,7 @@
       <c r="R9" s="21"/>
       <c r="S9" s="23"/>
     </row>
-    <row r="10" ht="97.23" customHeight="true">
+    <row r="10" ht="93.16" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -4775,7 +4775,7 @@
       <c r="R10" s="21"/>
       <c r="S10" s="24"/>
     </row>
-    <row r="11" ht="97.23" customHeight="true">
+    <row r="11" ht="93.16" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="S11" s="22"/>
     </row>
-    <row r="12" ht="97.23" customHeight="true">
+    <row r="12" ht="93.16" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
       <c r="R12" s="21"/>
       <c r="S12" s="23"/>
     </row>
-    <row r="13" ht="97.23" customHeight="true">
+    <row r="13" ht="93.16" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -4948,7 +4948,7 @@
       <c r="R13" s="21"/>
       <c r="S13" s="23"/>
     </row>
-    <row r="14" ht="97.23" customHeight="true">
+    <row r="14" ht="93.16" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -5003,7 +5003,7 @@
       <c r="R14" s="21"/>
       <c r="S14" s="24"/>
     </row>
-    <row r="15" ht="97.23" customHeight="true">
+    <row r="15" ht="93.16" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -5069,7 +5069,7 @@
       </c>
       <c r="S15" s="22"/>
     </row>
-    <row r="16" ht="97.23" customHeight="true">
+    <row r="16" ht="93.16" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="S16" s="23"/>
     </row>
-    <row r="17" ht="97.23" customHeight="true">
+    <row r="17" ht="93.16" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -5139,7 +5139,7 @@
       <c r="R17" s="21"/>
       <c r="S17" s="23"/>
     </row>
-    <row r="18" ht="97.23" customHeight="true">
+    <row r="18" ht="93.16" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -5176,6 +5176,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="46"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="48"/>
 </worksheet>
 </file>